--- a/exports/trend_1d/KAYNES_full_report.xlsx
+++ b/exports/trend_1d/KAYNES_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.79</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H2" t="n">
-        <v>2456.05</v>
+        <v>2341.1</v>
       </c>
       <c r="I2" t="n">
         <v>2351.675719209511</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>231.94</v>
+        <v>216.41</v>
       </c>
       <c r="L2" t="n">
         <v>9.880000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>18.89</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45274</v>
+        <v>45275</v>
       </c>
       <c r="H3" t="n">
-        <v>2474.25</v>
+        <v>2580.45</v>
       </c>
       <c r="I3" t="n">
         <v>2559.241706939761</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.69</v>
+        <v>-10.22</v>
       </c>
       <c r="L3" t="n">
-        <v>8.92</v>
+        <v>12.98</v>
       </c>
       <c r="M3" t="n">
         <v>1.87</v>
       </c>
       <c r="N3" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="O3" t="n">
         <v>-4.68</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>10.38</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45364</v>
+        <v>45365</v>
       </c>
       <c r="H4" t="n">
-        <v>2784.05</v>
+        <v>2721.4</v>
       </c>
       <c r="I4" t="n">
         <v>2750.710186153301</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>7.89</v>
+        <v>5.46</v>
       </c>
       <c r="L4" t="n">
         <v>5.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.34</v>
+        <v>3.02</v>
       </c>
       <c r="N4" t="n">
         <v>5.93</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>18.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="H5" t="n">
-        <v>2567.35</v>
+        <v>3080.35</v>
       </c>
       <c r="I5" t="n">
         <v>2783.77846699367</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>5.66</v>
+        <v>-13.19</v>
       </c>
       <c r="L5" t="n">
-        <v>6.56</v>
+        <v>13.21</v>
       </c>
       <c r="M5" t="n">
-        <v>1.84</v>
+        <v>14.9</v>
       </c>
       <c r="N5" t="n">
-        <v>4.74</v>
+        <v>19.98</v>
       </c>
       <c r="O5" t="n">
         <v>-2.25</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>18.19</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H6" t="n">
-        <v>3517.5</v>
+        <v>2836.8</v>
       </c>
       <c r="I6" t="n">
         <v>3015.61925152724</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>14.19</v>
+        <v>-7.91</v>
       </c>
       <c r="L6" t="n">
-        <v>8.57</v>
+        <v>8.65</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.42</v>
+        <v>19.35</v>
       </c>
       <c r="O6" t="n">
         <v>19.98</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>34.72</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H7" t="n">
-        <v>3636.15</v>
+        <v>3721.35</v>
       </c>
       <c r="I7" t="n">
         <v>3695.070156262936</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-28.18</v>
+        <v>-31.18</v>
       </c>
       <c r="L7" t="n">
         <v>33.07</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>18.61</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H8" t="n">
-        <v>5048.5</v>
+        <v>4870.8</v>
       </c>
       <c r="I8" t="n">
         <v>4919.278484029775</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K8" t="n">
-        <v>35.66</v>
+        <v>30.89</v>
       </c>
       <c r="L8" t="n">
         <v>2.59</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>16.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H9" t="n">
-        <v>5682.3</v>
+        <v>5714.25</v>
       </c>
       <c r="I9" t="n">
         <v>5687.424164043423</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.66</v>
+        <v>-17.32</v>
       </c>
       <c r="L9" t="n">
-        <v>18.16</v>
+        <v>21.33</v>
       </c>
       <c r="M9" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>7.85</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H10" t="n">
-        <v>6672.35</v>
+        <v>6145.35</v>
       </c>
       <c r="I10" t="n">
         <v>6630.828654737838</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K10" t="n">
-        <v>16.77</v>
+        <v>7.54</v>
       </c>
       <c r="L10" t="n">
         <v>9.779999999999999</v>
@@ -1011,7 +1130,7 @@
         <v>1.78</v>
       </c>
       <c r="N10" t="n">
-        <v>5.08</v>
+        <v>7.9</v>
       </c>
       <c r="O10" t="n">
         <v>0.5600000000000001</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>20.12</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H11" t="n">
-        <v>4848.3</v>
+        <v>5036.4</v>
       </c>
       <c r="I11" t="n">
         <v>4891.575719409561</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>21.11</v>
+        <v>18.05</v>
       </c>
       <c r="L11" t="n">
         <v>9.84</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>15.16</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="H12" t="n">
-        <v>5583.5</v>
+        <v>5576</v>
       </c>
       <c r="I12" t="n">
         <v>5583.241365436291</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K12" t="n">
-        <v>10.86</v>
+        <v>10.71</v>
       </c>
       <c r="L12" t="n">
         <v>22.56</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="H13" t="n">
-        <v>5867.5</v>
+        <v>6095</v>
       </c>
       <c r="I13" t="n">
         <v>5982.635382511343</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.23</v>
+        <v>-9.31</v>
       </c>
       <c r="L13" t="n">
-        <v>6.62</v>
+        <v>11.99</v>
       </c>
       <c r="M13" t="n">
         <v>3.8</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>10.21</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="H14" t="n">
-        <v>5747.5</v>
+        <v>5660.5</v>
       </c>
       <c r="I14" t="n">
         <v>5663.160692493225</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.7</v>
+        <v>-7.13</v>
       </c>
       <c r="L14" t="n">
-        <v>6.1</v>
+        <v>7.38</v>
       </c>
       <c r="M14" t="n">
         <v>0.44</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H15" t="n">
-        <v>5638</v>
+        <v>6172</v>
       </c>
       <c r="I15" t="n">
         <v>5980.74492731705</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>2.72</v>
+        <v>11.01</v>
       </c>
       <c r="M15" t="n">
         <v>0.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-1.51</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16.3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="H16" t="n">
-        <v>7102</v>
+        <v>6838.5</v>
       </c>
       <c r="I16" t="n">
         <v>6916.596090775881</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K16" t="n">
-        <v>15.07</v>
+        <v>10.8</v>
       </c>
       <c r="L16" t="n">
         <v>11.26</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>12.07</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H17" t="n">
-        <v>3700.3</v>
+        <v>3943.7</v>
       </c>
       <c r="I17" t="n">
         <v>3801.443209751513</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K17" t="n">
-        <v>45.89</v>
+        <v>42.33</v>
       </c>
       <c r="L17" t="n">
         <v>4.36</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>19.06</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H18" t="n">
-        <v>3700.3</v>
+        <v>3475.6</v>
       </c>
       <c r="I18" t="n">
         <v>3492.489634373534</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.17</v>
+        <v>-11.87</v>
       </c>
       <c r="L18" t="n">
-        <v>9.07</v>
+        <v>12.37</v>
       </c>
       <c r="M18" t="n">
         <v>4.81</v>
       </c>
       <c r="N18" t="n">
-        <v>4.41</v>
+        <v>6.07</v>
       </c>
       <c r="O18" t="n">
         <v>6.58</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>17.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H19" t="n">
-        <v>3878.6</v>
+        <v>4016.8</v>
       </c>
       <c r="I19" t="n">
         <v>3983.153989735659</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.6</v>
+        <v>-15.57</v>
       </c>
       <c r="L19" t="n">
-        <v>14.37</v>
+        <v>17.07</v>
       </c>
       <c r="M19" t="n">
         <v>5.83</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.48</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H20" t="n">
-        <v>4178.4</v>
+        <v>3336.5</v>
       </c>
       <c r="I20" t="n">
         <v>3989.284097585826</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>4.02</v>
+        <v>-16.94</v>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>17.83</v>
       </c>
       <c r="M20" t="n">
-        <v>0.52</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>7.22</v>
+        <v>20.15</v>
       </c>
       <c r="O20" t="n">
         <v>3.56</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>27.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="H21" t="n">
-        <v>3210.7</v>
+        <v>3429.1</v>
       </c>
       <c r="I21" t="n">
         <v>3419.361601139609</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K21" t="n">
-        <v>3.77</v>
+        <v>-2.78</v>
       </c>
       <c r="L21" t="n">
         <v>12.71</v>
@@ -1638,7 +1889,7 @@
         <v>2.14</v>
       </c>
       <c r="N21" t="n">
-        <v>5.79</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
         <v>-20.15</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>13.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H22" t="n">
-        <v>3685</v>
+        <v>3600.5</v>
       </c>
       <c r="I22" t="n">
         <v>3636.416336932686</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>7.46</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>8.69</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1755,6 +2030,14 @@
       <c r="Q23" t="n">
         <v>39</v>
       </c>
+      <c r="R23" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3517,7 +3800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -3527,7 +3810,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -3537,7 +3820,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8">
@@ -3547,7 +3830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3557,7 +3840,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -3567,7 +3850,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -3607,7 +3890,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.26</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="15">
@@ -3617,7 +3900,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.18</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="16">
@@ -3627,7 +3910,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.95</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="17">
@@ -3637,7 +3920,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>231.94</v>
+        <v>216.41</v>
       </c>
     </row>
     <row r="18">
@@ -3647,7 +3930,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
@@ -3657,7 +3940,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.16</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="20">
@@ -3667,7 +3950,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.92</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="21">
@@ -3687,7 +3970,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -3697,7 +3980,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -3707,7 +3990,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.31</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="25">
@@ -3727,7 +4010,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.67</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="27">
@@ -3737,7 +4020,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.76</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="28">
@@ -3747,7 +4030,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
